--- a/Tools/Luban/DataTables/Datas/Language.xlsx
+++ b/Tools/Luban/DataTables/Datas/Language.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2a4156734c294b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R139b001217d04f8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1354,6 +1354,69 @@
         <x:v>继续</x:v>
       </x:c>
     </x:row>
+    <x:row r="57">
+      <x:c r="A57"/>
+      <x:c r="B57" t="str">
+        <x:v>LAUNCH_TITLE</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>墨法奇书</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58"/>
+      <x:c r="B58" t="str">
+        <x:v>LAUNCH_AWAKEN</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>正在唤醒魔法书……</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59"/>
+      <x:c r="B59" t="str">
+        <x:v>LAUNCH_RESOURCES</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>正在铺展书页……</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60"/>
+      <x:c r="B60" t="str">
+        <x:v>LAUNCH_UPDATE</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>正在准备魔法篇章……</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61"/>
+      <x:c r="B61" t="str">
+        <x:v>LAUNCH_SYSTEMS</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>正在注入魔法墨水……</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62"/>
+      <x:c r="B62" t="str">
+        <x:v>LAUNCH_ENTER</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>正在翻开新的篇章……</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63" t="str">
+        <x:v>LAUNCH_FAILURE</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>书页未能展开，请重新启动游戏</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
